--- a/Results_2a/Results_Alpha001/Results_SegRec/Results_Cross/Results_MSVT_SE_SE_Net_Wout_Aux/seed_results_MSVT_SE_SE_Net_balanced_subjects.xlsx
+++ b/Results_2a/Results_Alpha001/Results_SegRec/Results_Cross/Results_MSVT_SE_SE_Net_Wout_Aux/seed_results_MSVT_SE_SE_Net_balanced_subjects.xlsx
@@ -490,34 +490,34 @@
         <v>42</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.58</v>
+        <v>57.64</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8100000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.97</v>
+        <v>96.88</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.97</v>
+        <v>96.88</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>49.65</v>
       </c>
       <c r="I2" t="n">
-        <v>0.87</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="K2" t="n">
-        <v>0.71</v>
+        <v>71.1422</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>71</v>
       </c>
       <c r="B3" t="n">
-        <v>0.96</v>
+        <v>96.17999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.13</v>
+        <v>13.19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5600000000000001</v>
+        <v>55.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.95</v>
+        <v>94.78999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.61</v>
+        <v>60.76000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.12</v>
+        <v>12.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.92</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.91</v>
+        <v>90.62</v>
       </c>
       <c r="K3" t="n">
-        <v>0.57</v>
+        <v>57.3278</v>
       </c>
     </row>
     <row r="4">
@@ -560,34 +560,34 @@
         <v>101</v>
       </c>
       <c r="B4" t="n">
-        <v>0.89</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3</v>
+        <v>29.86</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8100000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="E4" t="n">
-        <v>0.96</v>
+        <v>95.83</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.97</v>
+        <v>96.88</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09</v>
+        <v>9.379999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.89</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.96</v>
+        <v>95.83</v>
       </c>
       <c r="K4" t="n">
-        <v>0.65</v>
+        <v>65.27889999999999</v>
       </c>
     </row>
     <row r="5">
@@ -595,34 +595,34 @@
         <v>113</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.44</v>
       </c>
       <c r="C5" t="n">
-        <v>0.34</v>
+        <v>33.68</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.96</v>
+        <v>95.83</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12</v>
+        <v>12.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.98</v>
+        <v>97.92</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2</v>
+        <v>20.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.97</v>
+        <v>96.88</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>89.58</v>
       </c>
       <c r="K5" t="n">
-        <v>0.71</v>
+        <v>70.6011</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
         <v>127</v>
       </c>
       <c r="B6" t="n">
-        <v>0.89</v>
+        <v>88.89</v>
       </c>
       <c r="C6" t="n">
-        <v>0.19</v>
+        <v>19.44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.65</v>
+        <v>65.28</v>
       </c>
       <c r="E6" t="n">
-        <v>0.96</v>
+        <v>96.17999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.97</v>
+        <v>96.53</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
       <c r="I6" t="n">
-        <v>0.88</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.71</v>
+        <v>71.17999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.59</v>
+        <v>58.6811</v>
       </c>
     </row>
     <row r="7">
@@ -665,34 +665,34 @@
         <v>131</v>
       </c>
       <c r="B7" t="n">
-        <v>0.93</v>
+        <v>92.71000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.57</v>
+        <v>57.29</v>
       </c>
       <c r="D7" t="n">
-        <v>0.74</v>
+        <v>73.61</v>
       </c>
       <c r="E7" t="n">
-        <v>0.97</v>
+        <v>96.53</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>9.719999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.91</v>
+        <v>90.62</v>
       </c>
       <c r="K7" t="n">
-        <v>0.68</v>
+        <v>67.5522</v>
       </c>
     </row>
     <row r="8">
@@ -700,34 +700,34 @@
         <v>139</v>
       </c>
       <c r="B8" t="n">
-        <v>0.47</v>
+        <v>47.22</v>
       </c>
       <c r="C8" t="n">
-        <v>0.37</v>
+        <v>36.81</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>79.86</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9399999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>89.58</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01</v>
+        <v>1.39</v>
       </c>
       <c r="I8" t="n">
-        <v>0.87</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.58</v>
+        <v>58.2167</v>
       </c>
     </row>
     <row r="9">
@@ -735,34 +735,34 @@
         <v>149</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9399999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="C9" t="n">
-        <v>0.57</v>
+        <v>57.29</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.91</v>
+        <v>90.62</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.96</v>
+        <v>95.83</v>
       </c>
       <c r="H9" t="n">
-        <v>0.22</v>
+        <v>22.22</v>
       </c>
       <c r="I9" t="n">
-        <v>0.98</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.97</v>
+        <v>96.53</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7</v>
+        <v>69.9833</v>
       </c>
     </row>
     <row r="10">
@@ -770,34 +770,34 @@
         <v>157</v>
       </c>
       <c r="B10" t="n">
-        <v>0.83</v>
+        <v>83.33</v>
       </c>
       <c r="C10" t="n">
-        <v>0.72</v>
+        <v>71.53</v>
       </c>
       <c r="D10" t="n">
-        <v>0.82</v>
+        <v>82.28999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.95</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>90.62</v>
       </c>
       <c r="G10" t="n">
-        <v>0.97</v>
+        <v>97.22</v>
       </c>
       <c r="H10" t="n">
-        <v>0.59</v>
+        <v>59.38</v>
       </c>
       <c r="I10" t="n">
-        <v>0.95</v>
+        <v>95.14</v>
       </c>
       <c r="J10" t="n">
-        <v>0.95</v>
+        <v>95.14</v>
       </c>
       <c r="K10" t="n">
-        <v>0.85</v>
+        <v>85.5711</v>
       </c>
     </row>
     <row r="11">
@@ -805,34 +805,34 @@
         <v>163</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9</v>
+        <v>89.92999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.52</v>
+        <v>51.73999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6899999999999999</v>
+        <v>69.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0.97</v>
+        <v>97.22</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>0.97</v>
+        <v>96.88</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07000000000000001</v>
+        <v>6.94</v>
       </c>
       <c r="I11" t="n">
-        <v>0.79</v>
+        <v>78.82000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.92</v>
+        <v>92.36</v>
       </c>
       <c r="K11" t="n">
-        <v>0.65</v>
+        <v>64.93000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -840,34 +840,34 @@
         <v>173</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8100000000000001</v>
+        <v>81.25</v>
       </c>
       <c r="C12" t="n">
-        <v>0.36</v>
+        <v>36.11</v>
       </c>
       <c r="D12" t="n">
-        <v>0.77</v>
+        <v>77.42999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.96</v>
+        <v>96.17999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.96</v>
+        <v>96.17999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.32</v>
+        <v>31.94</v>
       </c>
       <c r="I12" t="n">
-        <v>0.93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.99</v>
+        <v>98.61</v>
       </c>
       <c r="K12" t="n">
-        <v>0.68</v>
+        <v>67.97669999999999</v>
       </c>
     </row>
     <row r="13">
@@ -875,34 +875,34 @@
         <v>181</v>
       </c>
       <c r="B13" t="n">
-        <v>0.88</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>0.18</v>
+        <v>18.4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6899999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.98</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.92</v>
+        <v>92.36</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.89</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.61</v>
+        <v>61.0333</v>
       </c>
     </row>
     <row r="14">
@@ -910,34 +910,34 @@
         <v>322</v>
       </c>
       <c r="B14" t="n">
-        <v>0.86</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>0.16</v>
+        <v>16.32</v>
       </c>
       <c r="D14" t="n">
-        <v>0.72</v>
+        <v>72.22</v>
       </c>
       <c r="E14" t="n">
-        <v>0.96</v>
+        <v>96.17999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.93</v>
+        <v>93.06</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.86</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.66</v>
+        <v>65.97</v>
       </c>
       <c r="K14" t="n">
-        <v>0.57</v>
+        <v>57.2522</v>
       </c>
     </row>
     <row r="15">
@@ -945,34 +945,34 @@
         <v>521</v>
       </c>
       <c r="B15" t="n">
-        <v>0.93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.45</v>
+        <v>44.79</v>
       </c>
       <c r="D15" t="n">
-        <v>0.85</v>
+        <v>84.72</v>
       </c>
       <c r="E15" t="n">
-        <v>0.99</v>
+        <v>98.61</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.98</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.57</v>
+        <v>57.29</v>
       </c>
       <c r="I15" t="n">
-        <v>0.95</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.74</v>
+        <v>74.15000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -982,34 +982,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.86</v>
+        <v>85.9614</v>
       </c>
       <c r="C16" t="n">
-        <v>0.39</v>
+        <v>38.8636</v>
       </c>
       <c r="D16" t="n">
-        <v>0.76</v>
+        <v>75.7929</v>
       </c>
       <c r="E16" t="n">
-        <v>0.96</v>
+        <v>95.88209999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08</v>
+        <v>7.6864</v>
       </c>
       <c r="G16" t="n">
-        <v>0.93</v>
+        <v>92.98139999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2</v>
+        <v>20.2871</v>
       </c>
       <c r="I16" t="n">
-        <v>0.91</v>
+        <v>90.69929999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9</v>
+        <v>89.50790000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.67</v>
+        <v>66.40689999999999</v>
       </c>
     </row>
   </sheetData>
